--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_magallanes_y_la_antartica_chilena.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.52573037337887</v>
+      </c>
+      <c r="C2">
         <v>30.40453223796557</v>
-      </c>
-      <c r="C2">
-        <v>27.52573037337887</v>
       </c>
       <c r="D2">
         <v>3.288983340290691</v>
       </c>
       <c r="E2">
+        <v>17.42904109589041</v>
+      </c>
+      <c r="F2">
+        <v>63.31908675799086</v>
+      </c>
+      <c r="G2">
         <v>19.25187214611872</v>
-      </c>
-      <c r="F2">
-        <v>63.31908675799087</v>
-      </c>
-      <c r="G2">
-        <v>17.42904109589041</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>29.46428571428572</v>
+      </c>
+      <c r="C3">
         <v>35.71428571428572</v>
-      </c>
-      <c r="C3">
-        <v>29.46428571428572</v>
       </c>
       <c r="D3">
         <v>2.8</v>
       </c>
       <c r="E3">
-        <v>21.62162162162162</v>
+        <v>17.83783783783784</v>
       </c>
       <c r="F3">
         <v>60.54054054054053</v>
       </c>
       <c r="G3">
-        <v>17.83783783783784</v>
+        <v>21.62162162162162</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>13</v>
+      </c>
+      <c r="C4">
         <v>37</v>
-      </c>
-      <c r="C4">
-        <v>13</v>
       </c>
       <c r="D4">
         <v>2.702702702702703</v>
       </c>
       <c r="E4">
-        <v>24.66666666666667</v>
+        <v>8.666666666666666</v>
       </c>
       <c r="F4">
         <v>66.66666666666667</v>
       </c>
       <c r="G4">
-        <v>8.666666666666666</v>
+        <v>24.66666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>36.42857142857142</v>
+      </c>
+      <c r="C5">
         <v>22.85714285714286</v>
-      </c>
-      <c r="C5">
-        <v>36.42857142857142</v>
       </c>
       <c r="D5">
         <v>4.375</v>
       </c>
       <c r="E5">
-        <v>14.34977578475336</v>
+        <v>22.86995515695067</v>
       </c>
       <c r="F5">
         <v>62.78026905829596</v>
       </c>
       <c r="G5">
-        <v>22.86995515695067</v>
+        <v>14.34977578475336</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>39.71518987341772</v>
+      </c>
+      <c r="C6">
         <v>11.31329113924051</v>
-      </c>
-      <c r="C6">
-        <v>39.71518987341772</v>
       </c>
       <c r="D6">
         <v>8.839160839160838</v>
       </c>
       <c r="E6">
-        <v>7.49083289680461</v>
+        <v>26.29649030906234</v>
       </c>
       <c r="F6">
         <v>66.21267679413305</v>
       </c>
       <c r="G6">
-        <v>26.29649030906234</v>
+        <v>7.49083289680461</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>29.65596330275229</v>
+      </c>
+      <c r="C7">
         <v>25.80275229357798</v>
-      </c>
-      <c r="C7">
-        <v>29.65596330275229</v>
       </c>
       <c r="D7">
         <v>3.875555555555556</v>
       </c>
       <c r="E7">
-        <v>16.59781646503393</v>
+        <v>19.07642372381233</v>
       </c>
       <c r="F7">
         <v>64.32575981115373</v>
       </c>
       <c r="G7">
-        <v>19.07642372381233</v>
+        <v>16.59781646503393</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>39.44020356234097</v>
+      </c>
+      <c r="C8">
         <v>26.97201017811705</v>
-      </c>
-      <c r="C8">
-        <v>39.44020356234097</v>
       </c>
       <c r="D8">
         <v>3.707547169811321</v>
       </c>
       <c r="E8">
-        <v>16.20795107033639</v>
+        <v>23.70030581039755</v>
       </c>
       <c r="F8">
         <v>60.09174311926606</v>
       </c>
       <c r="G8">
-        <v>23.70030581039755</v>
+        <v>16.20795107033639</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>34.5679012345679</v>
+      </c>
+      <c r="C9">
         <v>22.22222222222222</v>
-      </c>
-      <c r="C9">
-        <v>34.5679012345679</v>
       </c>
       <c r="D9">
         <v>4.5</v>
       </c>
       <c r="E9">
-        <v>14.17322834645669</v>
+        <v>22.04724409448819</v>
       </c>
       <c r="F9">
         <v>63.77952755905512</v>
       </c>
       <c r="G9">
-        <v>22.04724409448819</v>
+        <v>14.17322834645669</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>27.2526158445441</v>
+      </c>
+      <c r="C10">
         <v>29.65022421524663</v>
-      </c>
-      <c r="C10">
-        <v>27.2526158445441</v>
       </c>
       <c r="D10">
         <v>3.372655777374471</v>
       </c>
       <c r="E10">
-        <v>18.89718771435104</v>
+        <v>17.36910296471306</v>
       </c>
       <c r="F10">
         <v>63.73370932093591</v>
       </c>
       <c r="G10">
-        <v>17.36910296471306</v>
+        <v>18.89718771435104</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>19.25925925925926</v>
+      </c>
+      <c r="C11">
         <v>14.81481481481481</v>
-      </c>
-      <c r="C11">
-        <v>19.25925925925926</v>
       </c>
       <c r="D11">
         <v>6.75</v>
       </c>
       <c r="E11">
-        <v>11.04972375690608</v>
+        <v>14.3646408839779</v>
       </c>
       <c r="F11">
         <v>74.58563535911603</v>
       </c>
       <c r="G11">
-        <v>14.3646408839779</v>
+        <v>11.04972375690608</v>
       </c>
     </row>
   </sheetData>
